--- a/information_forms/046_liquor_inventory_information_record_form--information_forms.xlsx
+++ b/information_forms/046_liquor_inventory_information_record_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>liquor_inventory_name</t>
+          <t>liquor_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>liquor_category</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liquor Category</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales_tax_rate</t>
+          <t>sales_price</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sales Tax Rate</t>
+          <t>Sales Price</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sales_price</t>
+          <t>purchase_quantity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sales Price</t>
+          <t>Purchase Quantity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>purchase_quantity</t>
+          <t>sales_quantity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Purchase Quantity</t>
+          <t>Sales Quantity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sales_quantity</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sales Quantity</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>liquor_inventory_name_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Liquor Name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>category_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>purchase_date_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Purchase Date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>purchase_price_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Purchase Price</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>sales_tax_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sales Tax</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sales_tax_rate_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sales Tax Rate</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sales_price_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sales Price</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>purchase_quantity_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Purchase Quantity</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sales_quantity_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sales Quantity</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>cost_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>notes_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>liquor_category_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1220,108 +921,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Liqueur</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>vodka</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Vodka</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rum</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Rum</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>whiskey</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Whiskey</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>gin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Gin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>tequila</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tequila</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>liqueur</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>Liqueur</t>
         </is>
